--- a/src/test/fixtures/adaptive-score-import.xlsx
+++ b/src/test/fixtures/adaptive-score-import.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camp Scores" sheetId="1" r:id="Rbef6ff0ebb6e4b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camp Scores" sheetId="1" r:id="R00dc3c2295804bc3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/src/test/fixtures/adaptive-score-import.xlsx
+++ b/src/test/fixtures/adaptive-score-import.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camp Scores" sheetId="1" r:id="R00dc3c2295804bc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camp Scores" sheetId="1" r:id="Rf37fa4f1b1934f73"/>
   </x:sheets>
 </x:workbook>
 </file>
